--- a/4999_Intercuenca_Alto_Apurimac/_raw_reportes_xlsx/IDConfig_67592_completo.xlsx
+++ b/4999_Intercuenca_Alto_Apurimac/_raw_reportes_xlsx/IDConfig_67592_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R6d728417a8ff4248"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rbec0a8fbedc84052"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.5437</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.5437</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.7136</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.7136</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.7136</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.7136</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.9382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.9382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.9382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -639,7 +774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     71.0123</x:v>
+        <x:v>     68.3228</x:v>
       </x:c>
     </x:row>
     <x:row>
